--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72474884</v>
+        <v>125660840</v>
       </c>
       <c r="B2" t="n">
-        <v>101219</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221978</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypericum montanum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,28 +703,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartedalen, 150 m SO om Brobacken, Boh</t>
+          <t>Stuvvikesjön, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328387.3793742573</v>
+        <v>328703</v>
       </c>
       <c r="R2" t="n">
-        <v>6459227.775012008</v>
+        <v>6459332</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I innerslänt glest.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,27 +781,872 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Emilia Fagerberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Emilia Fagerberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125662101</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brobacken, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>328332</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6459260</v>
+      </c>
+      <c r="S3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I ytterslänt på norra sidan om vägen.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>60622392</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103646</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brant vägskärning 150 m SO Brobacken, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>328388</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6459229</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>OB-Lil-0138</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-07-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I bergbrant på båda sidor vägen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren, Roger Gahnertz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72474884</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svartedalen, 150 m SO om Brobacken, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>328387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6459228</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Lars Erik Norbäck</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Lars Erik Norbäck, Roger Gahnertz</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125661804</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gropsjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>328431</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6459204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I klippbranten på östra sidan om vägen.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Maria Magnusson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125661828</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gropsjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>328400</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6459231</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Under klippbrant på östra sidan om vägen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125661915</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gropsjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>328376</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6459236</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Under klippbrant på östra sidan om vägen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>57182486</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stuvvik, väg O668, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>328488</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6459079</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>John Rolander Borlid</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gabriella Malmborg, Johanna Borlid</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1548,44 +1548,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57182486</v>
+        <v>135536511</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>103726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>221978</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bergjohannesört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stuvvik, väg O668, Boh</t>
+          <t>längs vägen N om Gropsjön, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>328488</v>
+        <v>328405</v>
       </c>
       <c r="R9" t="n">
-        <v>6459079</v>
+        <v>6459218</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,12 +1629,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-06-26</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-06-26</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,26 +1643,120 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Håkan Pleijel</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Pleijel, Lennart Bergstedt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>57182486</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stuvvik, väg O668, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>328488</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6459079</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>John Rolander Borlid</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Gabriella Malmborg, Johanna Borlid</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125660840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125662101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60622392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1161,6 +1181,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72474884</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,6 +1314,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661804</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1417,6 +1447,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661828</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1545,6 +1580,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125661915</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1659,6 +1699,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135536511</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1761,8 +1806,24 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57182486</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -1591,7 +1591,7 @@
         <v>135536511</v>
       </c>
       <c r="B9" t="n">
-        <v>103726</v>
+        <v>103777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -1591,7 +1591,7 @@
         <v>135536511</v>
       </c>
       <c r="B9" t="n">
-        <v>103777</v>
+        <v>103804</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,44 +1588,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57182486</v>
+        <v>135536511</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>103809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>221978</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bergjohannesört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stuvvik, väg O668, Boh</t>
+          <t>längs vägen N om Gropsjön, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>328488</v>
+        <v>328405</v>
       </c>
       <c r="R9" t="n">
-        <v>6459079</v>
+        <v>6459218</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1649,12 +1669,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-06-26</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-06-26</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,31 +1683,130 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Håkan Pleijel</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Pleijel, Lennart Bergstedt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135536511</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>57182486</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stuvvik, väg O668, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>328488</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6459079</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>John Rolander Borlid</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Gabriella Malmborg, Johanna Borlid</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/57182486</t>
         </is>
@@ -1703,6 +1822,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -1591,7 +1591,7 @@
         <v>135536511</v>
       </c>
       <c r="B9" t="n">
-        <v>103809</v>
+        <v>103811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -1591,7 +1591,7 @@
         <v>135536511</v>
       </c>
       <c r="B9" t="n">
-        <v>103811</v>
+        <v>103831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25655-2023 artfynd.xlsx
+++ b/artfynd/A 25655-2023 artfynd.xlsx
@@ -1591,7 +1591,7 @@
         <v>135536511</v>
       </c>
       <c r="B9" t="n">
-        <v>103831</v>
+        <v>103833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
